--- a/output/StructureDefinition-pdex-treatment-relationship.xlsx
+++ b/output/StructureDefinition-pdex-treatment-relationship.xlsx
@@ -521,10 +521,10 @@
     <t>Group.type</t>
   </si>
   <si>
-    <t>Type of group (provider treatment relationship)</t>
-  </si>
-  <si>
-    <t>Fixed to 'device' to represent a collection of providers with treatment relationships</t>
+    <t>Type of group (practitioners with treatment relationship)</t>
+  </si>
+  <si>
+    <t>Fixed to 'practitioner'. The Group's members are healthcare providers (Practitioner or PractitionerRole references) who have a treatment relationship with the member identified in Group.characteristic. Group.type SHALL reflect the type of entities in Group.member[]; per FHIR R4 the appropriate code for a group whose members are healthcare providers is 'practitioner'.</t>
   </si>
   <si>
     <t>Group members SHALL be of the appropriate resource type (Patient for person or animal; or Practitioner, Device, Medication or Substance for the other types.).</t>
@@ -533,7 +533,7 @@
     <t>Identifies what type of resources the group is made up of.</t>
   </si>
   <si>
-    <t>device</t>
+    <t>practitioner</t>
   </si>
   <si>
     <t>required</t>
@@ -639,14 +639,14 @@
     <t>Group.managingEntity</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1|RelatedPerson|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1)
+    <t xml:space="preserve">Reference(Organization)
 </t>
   </si>
   <si>
     <t>The Payer managing this treatment relationship</t>
   </si>
   <si>
-    <t>Reference to the Payer organization that is managing and maintaining this treatment relationship group</t>
+    <t>Reference to the Payer organization that is managing and maintaining this treatment relationship group. Constrained to Organization since the managing entity is always a Payer (i.e., a healthcare organization), not a Practitioner, PractitionerRole, or RelatedPerson.</t>
   </si>
   <si>
     <t>This does not strictly align with ownership of a herd or flock, but may suffice to represent that relationship in simple cases. More complex cases will require an extension.</t>
